--- a/tender-report/v3/output/20260519決標資料.xlsx
+++ b/tender-report/v3/output/20260519決標資料.xlsx
@@ -455,9 +455,9 @@
     <col width="44" customWidth="1" min="8" max="8"/>
     <col width="15.5" customWidth="1" min="9" max="9"/>
     <col width="15.5" customWidth="1" min="10" max="10"/>
-    <col width="42.5" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
     <col width="50" customWidth="1" min="12" max="12"/>
-    <col width="33.5" customWidth="1" min="13" max="13"/>
+    <col width="36.5" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="27.5" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
@@ -1551,10 +1551,14 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38229-115-034 112至115年度桃園市、新北市、基隆市、新竹縣、新竹市路邊停車費委託辦理智慧行動繳費服務案(後續擴充)</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
+          <t>38229-115-034</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>112至115年度桃園市、新北市、基隆市、新竹縣、新竹市路邊停車費委託辦理智慧行動繳費服務案(後續擴充)</t>
+        </is>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>限制性招標(未經公開評選或公開徵求)</t>
@@ -1562,7 +1566,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>&lt;勞務類&gt; 97 其他服務</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1570,35 +1574,127 @@
           <t>115/05/19</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>115/03/13</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4,862,000元 肆佰捌拾陸萬貳仟元</t>
+        </is>
+      </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,862,000</t>
+          <t>4,862,000元 肆佰捌拾陸萬貳仟元 決標金額是否係依預估條件估算之預估金額。 估算方式： 本採購案屬開口契約，依招標文件約定採購總金額上限為486萬2000元正，由機關視實際需要隨時通知得標廠商履約，並採契約單價及實際施作或供應之數量結算給付價金，故本案訂約時係以採購上限金額做為契約金額。</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
-      <c r="S7" s="2" t="inlineStr"/>
-      <c r="T7" s="2" t="inlineStr"/>
-      <c r="U7" s="2" t="inlineStr"/>
-      <c r="V7" s="2" t="inlineStr"/>
-      <c r="W7" s="2" t="inlineStr"/>
-      <c r="X7" s="2" t="inlineStr"/>
-      <c r="Y7" s="2" t="inlineStr"/>
-      <c r="Z7" s="2" t="inlineStr"/>
-      <c r="AA7" s="2" t="inlineStr"/>
-      <c r="AB7" s="2" t="inlineStr"/>
-      <c r="AC7" s="2" t="inlineStr"/>
-      <c r="AD7" s="2" t="inlineStr"/>
-      <c r="AE7" s="2" t="inlineStr"/>
-      <c r="AF7" s="2" t="inlineStr"/>
-      <c r="AG7" s="2" t="inlineStr"/>
-      <c r="AH7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>公告金額以上未達查核金額</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>最低標</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>決標公告</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>麻吉行得通股份有限公司 (PKLOTCORP INC.)</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>55762636</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>486,200元 肆拾捌萬陸仟貳佰元</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>中華民國(Republic of China (Taiwan))</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>115/07/01 － 116/06/30 (預估)</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>3.82.29</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>新北市政府交通局</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>220 新北市 板橋區 中山路一段161號10樓</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>楊媄華</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>(02) 29702960 # 8716</t>
+        </is>
+      </c>
+      <c r="AD7" s="2" t="inlineStr">
+        <is>
+          <t>(02) 29701110</t>
+        </is>
+      </c>
+      <c r="AE7" s="2" t="inlineStr">
+        <is>
+          <t>自辦</t>
+        </is>
+      </c>
+      <c r="AF7" s="2" t="inlineStr">
+        <is>
+          <t>新北市(非原住民地區)</t>
+        </is>
+      </c>
+      <c r="AG7" s="2" t="inlineStr">
+        <is>
+          <t>38229-115-034</t>
+        </is>
+      </c>
+      <c r="AH7" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="AI7" s="2" t="inlineStr">
         <is>
           <t>https://web.pcc.gov.tw/tps/atm/AtmAwardWithoutSso/QueryAtmAwardDetail?pkAtmMain=NzExODEyODU=</t>
@@ -1626,10 +1722,14 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>KLTP11503-01 基隆市過港路停車場第二期工程</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
+          <t>KLTP11503-01</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>基隆市過港路停車場第二期工程</t>
+        </is>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>公開招標</t>
@@ -1637,7 +1737,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>&lt;工程類&gt; 5139 其他土木工程</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1645,35 +1745,131 @@
           <t>115/05/19</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>115/05/15</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>24,225,776元 貳仟肆佰貳拾貳萬伍仟柒佰柒拾陸元</t>
+        </is>
+      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23,000,000</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr"/>
-      <c r="T8" s="2" t="inlineStr"/>
-      <c r="U8" s="2" t="inlineStr"/>
-      <c r="V8" s="2" t="inlineStr"/>
-      <c r="W8" s="2" t="inlineStr"/>
-      <c r="X8" s="2" t="inlineStr"/>
-      <c r="Y8" s="2" t="inlineStr"/>
-      <c r="Z8" s="2" t="inlineStr"/>
-      <c r="AA8" s="2" t="inlineStr"/>
-      <c r="AB8" s="2" t="inlineStr"/>
-      <c r="AC8" s="2" t="inlineStr"/>
-      <c r="AD8" s="2" t="inlineStr"/>
-      <c r="AE8" s="2" t="inlineStr"/>
-      <c r="AF8" s="2" t="inlineStr"/>
-      <c r="AG8" s="2" t="inlineStr"/>
-      <c r="AH8" s="2" t="inlineStr"/>
+          <t>23,000,000元 貳仟參佰萬元</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>23,498,000元 貳仟參佰肆拾玖萬捌仟元</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>公告金額以上未達查核金額</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>最低標 採購評選委員名單</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>決標公告</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>璟鑫營造股份有限公司</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>84240222</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>23,000,000元 貳仟參佰萬元</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>中華民國(Republic of China (Taiwan))</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>115/05/15 － 115/12/31 (預估)</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>3.76.57</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>交通處</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>202 基隆市 中正區 義一路一號</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>許淑聖</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>(02) 24261599 # 236</t>
+        </is>
+      </c>
+      <c r="AD8" s="2" t="inlineStr">
+        <is>
+          <t>(02) 24259116</t>
+        </is>
+      </c>
+      <c r="AE8" s="2" t="inlineStr">
+        <is>
+          <t>自辦</t>
+        </is>
+      </c>
+      <c r="AF8" s="2" t="inlineStr">
+        <is>
+          <t>基隆市(非原住民地區)</t>
+        </is>
+      </c>
+      <c r="AG8" s="2" t="inlineStr">
+        <is>
+          <t>KLTP1150301</t>
+        </is>
+      </c>
+      <c r="AH8" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="AI8" s="2" t="inlineStr">
         <is>
           <t>https://web.pcc.gov.tw/tps/atm/AtmAwardWithoutSso/QueryAtmAwardDetail?pkAtmMain=NzExODA3OTk=</t>
@@ -4489,14 +4685,10 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11504011</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>「個別藝文產業應用生成式人工智慧(AI)風險管理指引先導規劃暨相關法制策略規劃」藝文採購案</t>
-        </is>
-      </c>
+          <t>11504011 「個別藝文產業應用生成式人工智慧(AI)風險管理指引先導規劃暨相關法制策略規劃」藝文採購案</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
           <t>經公開評選或公開徵求之限制性招標</t>
@@ -4504,7 +4696,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>&lt;勞務類&gt; 96 娛樂,文化,體育服務</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -4512,127 +4704,35 @@
           <t>115/05/19</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>115/05/14</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>3,800,000元 參佰捌拾萬元</t>
-        </is>
-      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3,800,000元 參佰捌拾萬元</t>
+          <t>3,800,000</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>公告金額以上未達查核金額</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>準用最有利標 採購評選委員名單</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>決標公告</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>財團法人資訊工業策進會</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>05076416</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>3,800,000元 參佰捌拾萬元</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>中華民國(Republic of China (Taiwan))</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>否 預估分包予中小企業之金額： 0元</t>
-        </is>
-      </c>
-      <c r="X25" s="2" t="inlineStr">
-        <is>
-          <t>115/05/15 － 116/03/31</t>
-        </is>
-      </c>
-      <c r="Y25" s="2" t="inlineStr">
-        <is>
-          <t>A.25</t>
-        </is>
-      </c>
-      <c r="Z25" s="2" t="inlineStr">
-        <is>
-          <t>綜合規劃司</t>
-        </is>
-      </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>242 新北市 新莊區 中平路439號南棟13樓</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>陳鈺淇</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr">
-        <is>
-          <t>(02) 85126788</t>
-        </is>
-      </c>
-      <c r="AD25" s="2" t="inlineStr">
-        <is>
-          <t>(02) 89956412</t>
-        </is>
-      </c>
-      <c r="AE25" s="2" t="inlineStr">
-        <is>
-          <t>自辦</t>
-        </is>
-      </c>
-      <c r="AF25" s="2" t="inlineStr">
-        <is>
-          <t>新北市(非原住民地區)</t>
-        </is>
-      </c>
-      <c r="AG25" s="2" t="inlineStr">
-        <is>
-          <t>11504011</t>
-        </is>
-      </c>
-      <c r="AH25" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr"/>
+      <c r="W25" s="2" t="inlineStr"/>
+      <c r="X25" s="2" t="inlineStr"/>
+      <c r="Y25" s="2" t="inlineStr"/>
+      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="AA25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr"/>
+      <c r="AE25" s="2" t="inlineStr"/>
+      <c r="AF25" s="2" t="inlineStr"/>
+      <c r="AG25" s="2" t="inlineStr"/>
+      <c r="AH25" s="2" t="inlineStr"/>
       <c r="AI25" s="2" t="inlineStr">
         <is>
           <t>https://web.pcc.gov.tw/tps/atm/AtmAwardWithoutSso/QueryAtmAwardDetail?pkAtmMain=NzExODE0NTQ=</t>
@@ -5171,26 +5271,27 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
